--- a/ui_runner/templates/graded_analysis_tabs_2026-06-25.xlsx
+++ b/ui_runner/templates/graded_analysis_tabs_2026-06-25.xlsx
@@ -471,16 +471,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G2" t="n">
-        <v>69</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="3">
@@ -529,16 +529,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>202</v>
+        <v>251</v>
       </c>
       <c r="E4" t="n">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="F4" t="n">
-        <v>101</v>
+        <v>133</v>
       </c>
       <c r="G4" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5">
@@ -613,16 +613,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>125</v>
+        <v>144</v>
       </c>
       <c r="E7" t="n">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="F7" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G7" t="n">
-        <v>53.6</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="8">
@@ -642,16 +642,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>358</v>
+        <v>188</v>
       </c>
       <c r="E8" t="n">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="F8" t="n">
-        <v>234</v>
+        <v>80</v>
       </c>
       <c r="G8" t="n">
-        <v>34.6</v>
+        <v>57.4</v>
       </c>
     </row>
     <row r="9">
@@ -671,16 +671,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E9" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F9" t="n">
         <v>79</v>
       </c>
       <c r="G9" t="n">
-        <v>47</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="10">
@@ -700,16 +700,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>232</v>
+        <v>186</v>
       </c>
       <c r="E10" t="n">
         <v>131</v>
       </c>
       <c r="F10" t="n">
-        <v>101</v>
+        <v>55</v>
       </c>
       <c r="G10" t="n">
-        <v>56.5</v>
+        <v>70.40000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -729,16 +729,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>764</v>
+        <v>908</v>
       </c>
       <c r="E11" t="n">
-        <v>484</v>
+        <v>539</v>
       </c>
       <c r="F11" t="n">
-        <v>280</v>
+        <v>369</v>
       </c>
       <c r="G11" t="n">
-        <v>63.4</v>
+        <v>59.4</v>
       </c>
     </row>
     <row r="12">
@@ -758,16 +758,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>742</v>
       </c>
       <c r="E12" t="n">
-        <v>108</v>
+        <v>291</v>
       </c>
       <c r="F12" t="n">
-        <v>53</v>
+        <v>451</v>
       </c>
       <c r="G12" t="n">
-        <v>67.09999999999999</v>
+        <v>39.2</v>
       </c>
     </row>
     <row r="13">
@@ -787,16 +787,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="E13" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F13" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="G13" t="n">
-        <v>60.3</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="14">
@@ -816,16 +816,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>245</v>
+        <v>525</v>
       </c>
       <c r="E14" t="n">
-        <v>75</v>
+        <v>102</v>
       </c>
       <c r="F14" t="n">
-        <v>170</v>
+        <v>423</v>
       </c>
       <c r="G14" t="n">
-        <v>30.6</v>
+        <v>19.4</v>
       </c>
     </row>
     <row r="15">
@@ -845,16 +845,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>287</v>
+        <v>2061</v>
       </c>
       <c r="E15" t="n">
-        <v>59</v>
+        <v>199</v>
       </c>
       <c r="F15" t="n">
-        <v>228</v>
+        <v>1862</v>
       </c>
       <c r="G15" t="n">
-        <v>20.6</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -874,16 +874,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>169</v>
+        <v>197</v>
       </c>
       <c r="E16" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F16" t="n">
-        <v>140</v>
+        <v>164</v>
       </c>
       <c r="G16" t="n">
-        <v>17.2</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="17">
@@ -903,16 +903,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>5062</v>
+        <v>3284</v>
       </c>
       <c r="E17" t="n">
-        <v>833</v>
+        <v>574</v>
       </c>
       <c r="F17" t="n">
-        <v>4229</v>
+        <v>2710</v>
       </c>
       <c r="G17" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
     </row>
   </sheetData>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>68.8</v>
+        <v>91.7</v>
       </c>
       <c r="C2" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D2" t="n">
         <v>62.5</v>
@@ -1115,10 +1115,10 @@
         <v>8</v>
       </c>
       <c r="F2" t="n">
-        <v>50</v>
+        <v>24.4</v>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="H2" t="n">
         <v>25</v>
@@ -1126,23 +1126,23 @@
       <c r="I2" t="n">
         <v>4</v>
       </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="L2" t="n">
-        <v>100</v>
+        <v>5.4</v>
       </c>
       <c r="M2" t="n">
-        <v>4</v>
+        <v>112</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="P2" t="n">
-        <v>6.2</v>
-      </c>
       <c r="Q2" t="n">
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -1154,10 +1154,10 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>50</v>
+        <v>84.2</v>
       </c>
       <c r="Y2" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
@@ -1182,49 +1182,49 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45.8</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="D3" t="n">
-        <v>65</v>
+        <v>63.6</v>
       </c>
       <c r="E3" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F3" t="n">
-        <v>63.6</v>
+        <v>32.2</v>
       </c>
       <c r="G3" t="n">
-        <v>11</v>
+        <v>208</v>
       </c>
       <c r="H3" t="n">
-        <v>60</v>
+        <v>33.3</v>
       </c>
       <c r="I3" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J3" t="n">
-        <v>25</v>
+        <v>7.5</v>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>93</v>
       </c>
       <c r="L3" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="M3" t="n">
-        <v>4</v>
+        <v>657</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>14.5</v>
+        <v>44.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>884</v>
+        <v>18</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1236,10 +1236,10 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>21</v>
+        <v>43.6</v>
       </c>
       <c r="Y3" t="n">
-        <v>100</v>
+        <v>39</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -1355,10 +1355,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>48.3</v>
+        <v>56</v>
       </c>
       <c r="C5" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="D5" t="n">
         <v>65.40000000000001</v>
@@ -1367,28 +1367,28 @@
         <v>26</v>
       </c>
       <c r="F5" t="n">
-        <v>50</v>
+        <v>33.6</v>
       </c>
       <c r="G5" t="n">
-        <v>16</v>
+        <v>113</v>
       </c>
       <c r="H5" t="n">
-        <v>16.7</v>
+        <v>14.3</v>
       </c>
       <c r="I5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J5" t="n">
-        <v>50</v>
+        <v>16.3</v>
       </c>
       <c r="K5" t="n">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="L5" t="n">
-        <v>25</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>8</v>
+        <v>270</v>
       </c>
       <c r="N5" t="n">
         <v>33.3</v>
@@ -1397,10 +1397,10 @@
         <v>3</v>
       </c>
       <c r="P5" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>365</v>
+        <v>3</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1412,10 +1412,10 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>36.7</v>
+        <v>48.1</v>
       </c>
       <c r="Y5" t="n">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1440,10 +1440,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>46.9</v>
+        <v>56.5</v>
       </c>
       <c r="C6" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D6" t="n">
         <v>82.40000000000001</v>
@@ -1452,10 +1452,10 @@
         <v>17</v>
       </c>
       <c r="F6" t="n">
-        <v>85.7</v>
+        <v>40.9</v>
       </c>
       <c r="G6" t="n">
-        <v>7</v>
+        <v>93</v>
       </c>
       <c r="H6" t="n">
         <v>50</v>
@@ -1464,28 +1464,28 @@
         <v>2</v>
       </c>
       <c r="J6" t="n">
-        <v>25</v>
+        <v>18.9</v>
       </c>
       <c r="K6" t="n">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="L6" t="n">
-        <v>25</v>
+        <v>6.6</v>
       </c>
       <c r="M6" t="n">
-        <v>4</v>
+        <v>273</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="Q6" t="n">
-        <v>358</v>
+        <v>2</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1497,10 +1497,10 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>40</v>
+        <v>66.7</v>
       </c>
       <c r="Y6" t="n">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1525,73 +1525,73 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>56.5</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="C7" t="n">
-        <v>232</v>
+        <v>186</v>
       </c>
       <c r="D7" t="n">
-        <v>63.4</v>
+        <v>59.4</v>
       </c>
       <c r="E7" t="n">
-        <v>764</v>
+        <v>908</v>
       </c>
       <c r="F7" t="n">
-        <v>67.09999999999999</v>
+        <v>39.2</v>
       </c>
       <c r="G7" t="n">
-        <v>161</v>
+        <v>742</v>
       </c>
       <c r="H7" t="n">
-        <v>60.3</v>
+        <v>50.6</v>
       </c>
       <c r="I7" t="n">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="J7" t="n">
-        <v>30.6</v>
+        <v>19.4</v>
       </c>
       <c r="K7" t="n">
-        <v>245</v>
+        <v>525</v>
       </c>
       <c r="L7" t="n">
-        <v>20.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>287</v>
+        <v>2061</v>
       </c>
       <c r="N7" t="n">
-        <v>17.2</v>
+        <v>16.8</v>
       </c>
       <c r="O7" t="n">
-        <v>169</v>
+        <v>197</v>
       </c>
       <c r="P7" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>5062</v>
+        <v>3284</v>
       </c>
       <c r="R7" t="n">
-        <v>69</v>
+        <v>66.7</v>
       </c>
       <c r="S7" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="T7" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="U7" t="n">
-        <v>202</v>
+        <v>251</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>34.6</v>
+        <v>57.4</v>
       </c>
       <c r="Y7" t="n">
-        <v>358</v>
+        <v>188</v>
       </c>
       <c r="Z7" t="n">
         <v>50</v>
@@ -1606,16 +1606,16 @@
         <v>1</v>
       </c>
       <c r="AD7" t="n">
-        <v>53.6</v>
+        <v>56.2</v>
       </c>
       <c r="AE7" t="n">
-        <v>125</v>
+        <v>144</v>
       </c>
       <c r="AF7" t="n">
-        <v>47</v>
+        <v>47.7</v>
       </c>
       <c r="AG7" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>
